--- a/i_test/test_D6_Table_2/g_output/D6_Table_2_cohort_characteristics_subpopulation_CAP_SGLT2i.xlsx
+++ b/i_test/test_D6_Table_2/g_output/D6_Table_2_cohort_characteristics_subpopulation_CAP_SGLT2i.xlsx
@@ -518,47 +518,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>550</t>
+          <t>556</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>560</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>578</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>524</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>538</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>580</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>560</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>546</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>539</t>
+          <t>558</t>
         </is>
       </c>
     </row>
@@ -570,47 +570,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>269 (48,9%)</t>
+          <t>191 (34,4%)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>279 (50,5%)</t>
+          <t>217 (38,8%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>250 (49,5%)</t>
+          <t>176 (30,4%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>289 (52,8%)</t>
+          <t>177 (33,8%)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>297 (50,9%)</t>
+          <t>175 (32,5%)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>289 (49,4%)</t>
+          <t>187 (32,2%)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>253 (45,7%)</t>
+          <t>197 (35,2%)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>291 (49,8%)</t>
+          <t>186 (34,1%)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>268 (49,7%)</t>
+          <t>195 (34,9%)</t>
         </is>
       </c>
     </row>
@@ -622,47 +622,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20 (3,6%)</t>
+          <t>211 (37,9%)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12 (2,2%)</t>
+          <t>209 (37,3%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>15 (3,0%)</t>
+          <t>251 (43,4%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16 (2,9%)</t>
+          <t>204 (38,9%)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13 (2,2%)</t>
+          <t>206 (38,3%)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>20 (3,4%)</t>
+          <t>227 (39,1%)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>16 (2,9%)</t>
+          <t>222 (39,6%)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>21 (3,6%)</t>
+          <t>219 (40,1%)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>19 (3,5%)</t>
+          <t>223 (40,0%)</t>
         </is>
       </c>
     </row>
@@ -674,47 +674,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>261 (47,5%)</t>
+          <t>154 (27,7%)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>261 (47,3%)</t>
+          <t>134 (23,9%)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>240 (47,5%)</t>
+          <t>151 (26,1%)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>242 (44,2%)</t>
+          <t>143 (27,3%)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>274 (46,9%)</t>
+          <t>157 (29,2%)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>276 (47,2%)</t>
+          <t>166 (28,6%)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>285 (51,4%)</t>
+          <t>141 (25,2%)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>272 (46,6%)</t>
+          <t>141 (25,8%)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>252 (46,8%)</t>
+          <t>140 (25,1%)</t>
         </is>
       </c>
     </row>
@@ -726,47 +726,47 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>456 (82,9%)</t>
+          <t>498 (89,6%)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>472 (85,5%)</t>
+          <t>520 (92,9%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>418 (82,8%)</t>
+          <t>515 (89,1%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>455 (83,2%)</t>
+          <t>474 (90,5%)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>472 (80,8%)</t>
+          <t>491 (91,3%)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>492 (84,1%)</t>
+          <t>526 (90,7%)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>458 (82,7%)</t>
+          <t>522 (93,2%)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>489 (83,7%)</t>
+          <t>494 (90,5%)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>460 (85,3%)</t>
+          <t>506 (90,7%)</t>
         </is>
       </c>
     </row>
@@ -778,47 +778,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>119 (21,6%)</t>
+          <t>184 (33,1%)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>109 (19,7%)</t>
+          <t>171 (30,5%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>104 (20,6%)</t>
+          <t>157 (27,2%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>110 (20,1%)</t>
+          <t>158 (30,2%)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>130 (22,3%)</t>
+          <t>158 (29,4%)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>131 (22,4%)</t>
+          <t>190 (32,8%)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>103 (18,6%)</t>
+          <t>172 (30,7%)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>114 (19,5%)</t>
+          <t>170 (31,1%)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>118 (21,9%)</t>
+          <t>155 (27,8%)</t>
         </is>
       </c>
     </row>
